--- a/out/成願寺川_設計照査_現場技術員所見.xlsx
+++ b/out/成願寺川_設計照査_現場技術員所見.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>共通仕様書3-6
+          <t>共通仕様書3-6(工事中の安全確保)
 3)現場管理の留意事項(1)
 ※条文番号要確認</t>
         </is>
@@ -849,8 +849,7 @@
 　・浚渫土量（現況測量と設計横断の比較）
 　・残土の処分先と運搬距離
 　・濁水対策と関係機関（漁協等）との協議状況
-　・出水期の施工制限と工期の妥当性
-あわせて、照査結果様式の「⑥ 工事資料配布について」欄は内容と見出しが一致していないため、受注者に修正を求めることを提案する。</t>
+　・出水期の施工制限と工期の妥当性</t>
         </is>
       </c>
       <c r="D13" s="4" t="n"/>

--- a/out/成願寺川_設計照査_現場技術員所見.xlsx
+++ b/out/成願寺川_設計照査_現場技術員所見.xlsx
@@ -10,7 +10,7 @@
     <sheet name="照査所見" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'照査所見'!$7:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'照査所見'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +51,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,18 +97,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -108,8 +122,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,17 +499,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -498,409 +519,636 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>工事名</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>（記入）成願寺川　　　　工事</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>管内一円（成願寺川）緊急浚渫推進（砂防）工事</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>工事番号</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>丹後８緊急浚渫（砂防）第３９９９号の１の２</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>受注者</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>サンキ工業株式会社</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>照査結果</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>設計図書照査結果 No.1（質疑5件）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>受理日</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>設計図書照査結果 No.1（5件）</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>（記入）令和　年　月　日</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>現地確認日</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>（記入）令和　年　月　日</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>作成者</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">（記入）現場技術員　　　　　</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>【照査の判断基準】共通仕様書1-1-1-3：受注者は自らの負担により、契約書第18条第1項第1号〜第5号（①図面・仕様書等の不一致、②誤謬・脱漏、③表示が不明確、④施工条件と現場の不一致、⑤予期できない特別な状態）に係る設計図書の照査を行い、該当する事実がある場合は、その事実が確認できる資料を書面により提出し確認を求める。土木工事書類一覧表（設計図書）の備考：「契約書第18条第1項の範囲を超えないこと」。</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>照査対象</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>照査対象
+（受注者記載）</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>受注者の照査内容（要旨）</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>確認事項
-（設計図書・当初積算・現地）</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>第18条
+該当性</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>設計図書の該当規定</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>現場技術員 所見</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>区分（案）</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>受注者への追加資料要求</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>回答案（質疑として回答）</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>監督職員 判断欄</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="8" t="n">
+    <row r="10" ht="175" customHeight="1">
+      <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>特記仕様書3-6 1)
 事前調査における留意事項</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>過去に発生した土砂災害の発生状況について、事務所で把握・保管している情報の提示を求めるもの。</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>□ 事務所保有の災害履歴・点検記録の有無
-□ 提示可能な範囲（公開可否）</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>本件は特記仕様書3-6 1)に基づく情報提供の依頼であり、設計図書と現地条件の不一致を指摘する照査事項ではないと考えられる。
-発注者が保有する災害履歴・点検記録の有無を確認し、提示可能な範囲で提供することが望ましい。
-なお、回答欄の「設計変更／変更なし」には該当しないため、「情報提供」として回答することを提案する。</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>情報提供</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>特になし</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>過去に発生した土砂災害発生状況について、事務所で把握・保管している情報の提示を求めるもの。</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>該当せず
+（情報提供依頼）</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>特記3-6 1)(1)：工事対象渓流並びに周辺流域について、…過去に発生した土砂災害発生状況等、流域状況を調査すること（受注者が調査し、結果を記録する）。</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>設計図書の不一致等を示したものではなく、情報提供の依頼である。特記3-6 1)(1)により、土砂災害発生状況の調査は受注者が行うべき事項である。</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>土砂災害発生状況の調査は、特記仕様書3-6 1)(1)により受注者において実施されたい。なお、当事務所で保有する資料（　　　　）については参考として提供する。</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="175" customHeight="1">
+      <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>掘削工</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>上部水抜きから底部水抜きまでの掘削中、掘削底に水が溜まり、底部水抜き到達時に土砂が一気に流出するおそれがあるため、排水ポンプ・大型土のう・釜場の設置が設計変更の対象か確認するもの。</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>□ 当初設計の水替工計上の有無
-□ 仮設区分（指定／任意）
-□ 現地の湛水・流入状況</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>当初設計に水替工が計上されているか、また仮設が指定仮設か任意仮設かの確認が必要である。任意仮設の場合、原則として受注者の負担と考えられる。
-ただし、上流からの流入や湛水が設計条件を大きく超える場合は、条件変更（契約書第18条）の協議対象となり得る。
-また、水抜き到達時の土砂流出は下流への濁水影響も懸念されるため、濁水対策を含めて施工計画書に記載させることを推奨する。</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>要確認
-（任意仮設なら受注者負担、条件相違なら協議対象）</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>・湛水状況の写真
-・想定排水量
-・ポンプの規格・台数・稼働日数
-・大型土のうの配置図
-・濁水対策（施工計画書）</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>上部水抜きから底部水抜きまでの掘削中、掘削底に溜まった水により、底部水抜き到達時に土砂が一気に流出するおそれがあるため、排水ポンプ・大型土のうによる釜場設置が設計変更の対象か問うもの。</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>該当せず
+（施工方法・費用の質疑）</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>水替えに関する規定なし（契約書第1条第3項により任意仮設）。
+特記7-2（土砂流出防止装置）：砂防堰堤の排水口を計測及び確認の上、土砂流出防止装置の見積書を提出し、施工を行う。
+浚渫特記（施工準備等）3：利害関係者との調整結果により濁水処理に係る対策施設等が必要となった場合は協議し、設計変更の対象。</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>設計図書と現場条件の不一致は示されていない。水替え・釜場は施工方法（任意仮設）であり、原則として受注者の責による。
+懸念している底部水抜き到達時の土砂流出については、特記7-2の土砂流出防止装置との関係を整理させる必要がある。湛水状況が設計条件と著しく異なる場合は、その事実（写真・測定値）を添えて改めて照査として提出させる。</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>水替え・釜場は任意仮設であり、設計変更の対象としない。土砂流出対策は、特記仕様書7-2により排水口を計測・確認の上、土砂流出防止装置の見積書を提出されたい。現場条件が設計図書と異なる事実がある場合は、根拠資料を添えて改めて提出されたい。</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="175" customHeight="1">
+      <c r="A12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>河川浚渫工事に関する特記事項
 (施工準備等) 2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>掘削範囲内の立木の伐木・伐根費、伐木材の処分費、掘削土から出土した流木等の処分費が設計変更の対象か確認するもの（現況写真添付）。</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>□ 伐木除根・処分の計上有無
-□ 立木の本数・径・範囲
-□ 処分先・受入条件</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>設計図書に伐木・除根・処分が計上されていない場合、添付の現況写真で立木が確認できることから条件明示が不足していると考えられ、設計変更の対象となり得る。
-受注者との立会いで本数・胸高直径・範囲を確認し、記録しておくことを推奨する。
-流木は発生量を事前に確定できないため、実績数量で精算する方針を確認しておくことが望ましい。
-伐採木を産業廃棄物（木くず）として処分する場合の処分先と受入証明についても確認が必要である。</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>設計変更の対象となり得る
-（未計上の場合）</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>・立木の数量表（本数・胸高直径・範囲）
-・処分先と受入条件
-・流木の発生量記録（実績・写真）</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>掘削範囲内の立木伐木伐根費、伐木材の処分費、掘削土から出土した流木等の処分費が設計変更の対象か問うもの（現況写真添付）。</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>該当せず
+（設計図書に明示済み）</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>特記3-8：建設発生木材の運搬及び処分については、当初計上していないため、…協議するものとし、設計変更の対象とする。
+特記7-2（施工準備等）：除草作業は共通仮設費の率計算に含む。ただし、立木の伐採…は協議の上、設計変更の対象とする。
+特記7-2（工事用道路）：伐採が必要な場合は、必ず当該土地の地権者に伐採の可否を確認の上作業を行うこと。</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>取扱いは特記3-8・7-2に明示されており、照査事項には当たらない。設計変更の対象であることは図書から読み取れる。
+今後は協議に移り、伐採の本数・胸高直径・範囲と流木等の発生量を立会いで確認し、記録する必要がある。地権者の伐採可否の確認（特記7-2）が済んでいるかもあわせて確認する。</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>特記仕様書3-8及び7-2のとおり、協議の上、設計変更の対象とする。伐採範囲・数量（本数・胸高直径）及び発生木材・流木の数量が確認できる資料を工事打合せ簿（協議）により提出されたい。また、伐採にあたっては地権者に伐採の可否を確認すること。</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="175" customHeight="1">
+      <c r="A13" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>仮設工（敷鉄板）</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>当初設計（L=144.0m、100枚）に対し、カーブ・転回場所等に必要な追加枚数が設計変更の対象か確認するもの。</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>□ 仮設区分（指定／任意）
-□ 当初数量の算定条件（幅・板寸法）
-□ 転回場所の必要性（現地）</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>当初数量（L=144m、100枚）は、直線部を幅約3m（1.5m×3.0m板）で敷く場合に相当し、カーブ部や転回場所は計上されていないと考えられる。
-敷鉄板が指定仮設か任意仮設かを確認したうえで、転回場所が施工上欠かせないかを現地で確認する必要がある。
-必要と認められる場合は、配置図と枚数の算出根拠を提出させて協議することが望ましい。リース期間（賃料日数）が当初と変わるかもあわせて確認されたい。</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>要確認
-（必要性が認められれば協議対象）</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>・敷鉄板配置図
-・追加枚数の算出根拠
-・使用期間（賃料日数）</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>仮設工
+（敷鉄板）</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>当初設計（L=144.0m、100枚）に対し、カーブ・転回場所等に必要な枚数が設計変更の対象か問うもの。</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>該当せず
+（設計図書に明示済み）</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>特記7-2（工事用道路）：堰堤堆砂敷までの工事用道路について、当初設計においては、敷鉄板及び工事用道路を計上している。受注者は現地踏査において、工事用道路設置に必要な措置を検討するものとし、必要と認められる場合は監督員と協議の上、設計変更の対象とする。</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>取扱いは特記7-2に明示されており、照査事項には当たらない。
+現地踏査に基づく配置図・追加枚数・使用期間を提出させ、必要性を確認したうえで協議に移るのが妥当である。</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>特記仕様書7-2のとおり、現地踏査により必要な措置を検討し、必要と認められる場合は協議の上、設計変更の対象とする。敷鉄板の配置図、追加枚数の算出根拠及び使用期間を工事打合せ簿（協議）により提出されたい。</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="175" customHeight="1">
+      <c r="A14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>共通仕様書3-6(工事中の安全確保)
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>共通仕様書3-6
+(工事中の安全確保)
 3)現場管理の留意事項(1)
-※条文番号要確認</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>「警報設備を設け」とあるが、警報装置のリース料は共通仮設費に含まれるか確認するもの。</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>□ 引用条文の正誤
-□ 警報設備の用途
-□ 特記での別途計上の明示有無</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>引用条文「共通仕様書3-6 3)」は、No.1の記載との対応から「特記仕様書3-6 3)」の誤りと思われるため、受注者に確認を求める。
-警報設備の用途（出水時の水位警報か、重機接近の警報か等）を確認する必要がある。
-一般には積算基準上、共通仮設費率（安全費）に含まれると考えられる。ただし特記仕様書に別途計上の明示がある場合は積み上げ計上の対象となるため、積算担当への確認を推奨する。</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>共通仮設費（率）に含まれると考えられる
-（要積算確認）</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>・引用条文の訂正
-・警報設備の仕様・用途</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13" ht="130" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+※正しくは特記仕様書</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>「警報設備を設け」とあるが、警報装置のリース料は共通仮設費に含まれるか問うもの。</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>該当せず
+（積算の質疑）</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>特記3-6 3)(1)：土石流が発生した場合にすみやかにこれを知らせるための警報設備を設け、常に有効に機能するよう点検・整備を行うこと。
+特記3-4（安全対策費）：条件変更及び受注者にて特に必要と認めた場合は、その対策等について協議し、設計変更の対象とする。</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>積算内訳に関する質疑であり、照査事項には当たらない。
+引用条文は「共通仕様書3-6」ではなく「特記仕様書3-6」であり、訂正を求める。
+当初設計書における警報設備の計上の有無（共通仮設費率内か積上げか）を監督職員側で確認のうえ回答する必要がある。</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>警報設備の費用は、当初設計において（共通仮設費率に含む／積上げ計上：確認のうえ記入）。当初計上を超える設備が必要な場合は、特記仕様書3-4により、その内容を工事打合せ簿（協議）で提出されたい。なお、照査対象の記載は「特記仕様書3-6」に訂正すること。</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>受注者に実施を求める設計図書の照査（例）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>照査項目</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>第18条</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>確認内容</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>横断図・平面図と現況</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>設計図が標準断面図の場合、事前測量（横断測量）を実施し、堆積状況・掘削断面・河床勾配の相違を示して施工図を作成・提出する。</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>浚渫特記（事前測量）1・2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>図面と数量計算書の整合</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>①②</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>図面の掘削範囲・延長と数量計算書の掘削土量・残土量が一致しているか確認する。</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>共通仕様書1-1-1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>砂防堰堤の排水口</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>土砂流出防止装置の前提となる排水口の寸法・状態を現地で計測し、設計図書との相違を確認する。</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>特記7-2（土砂流出防止装置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>工事用道路・敷鉄板・借地</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>設計上の工事用道路ルート・敷鉄板範囲と、現地で必要な範囲との相違を配置図で示す。借地の要否を確認する。</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>特記7-2（工事用道路・借地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>支障物件</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>④⑤</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>搬入出路を含む区間内の電柱架線・上下水道・ガス管・樹木・既存構造物等を確認し、監督員に報告する。</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>特記2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>建設発生土の搬出</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>①④</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>土砂条例に基づく必要書類（試料採取位置図・写真、採取報告書（第4号様式）、分析結果証明書）と受入条件を確認する。</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>特記3-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>総括所見</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>今回の照査結果5件のうち4件は費用負担に関する質疑であり、照査の本来の対象である数量・図面の整合性については結果が示されていない。特に次の項目は、施工開始後に変更協議となる可能性が高いため、受注者に照査結果の追加提出を求めるか、監督職員側で事前に確認しておくことが望ましい。
-　・浚渫土量（現況測量と設計横断の比較）
-　・残土の処分先と運搬距離
-　・濁水対策と関係機関（漁協等）との協議状況
-　・出水期の施工制限と工期の妥当性</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>提出された照査結果5件は、いずれも契約書第18条第1項第1号〜第5号に該当する事実を示したものではなく、情報提供の依頼及び費用負担等に関する質疑である。特にNo.3・No.4は特記仕様書3-8・7-2に取扱いが明示されており、設計図書の確認が十分でないまま提出されたものと考えられる。
+よって、本件は質疑として回答することとし、受注者に対しては、共通仕様書1-1-1-3に基づく設計図書の照査（上表の例：図面・数量・現地条件の整合確認）を実施し、該当する事実がある場合は根拠資料を添えて改めて提出するよう求めることが望ましい。
+なお、No.3の伐採については、特記7-2により地権者への伐採可否の確認が必要であるが、地元打合せ（9月25日）では「用地は不明、関係者がいれば地区から伝える」にとどまっているため、受注者に地権者確認を指示する必要がある。</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>【凡例・注意】</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>・黄色のセルは記入欄です（工事名、日付、作成者、監督職員判断欄）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>・「確認事項」欄の□は、当初設計書・数量計算書・積算内訳・現地で確認した後にチェックしてください。確認結果に応じて所見の表現を修正してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>・所見は監督職員の判断材料であり、設計変更の可否を決定するものではありません。受注者への回答は監督職員を通じて行います。</t>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>・「特記」は本工事の特記仕様書、「浚渫特記」は同添付の「河川浚渫工事に関する特記事項」を指します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>・黄色のセルは記入欄です。No.1・No.5の回答案の（　）内は、当初設計書を確認のうえ記入してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>・所見及び回答案は監督職員の判断材料であり、受注者への回答は監督職員を通じて行います。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C13:H13"/>
+  <mergeCells count="32">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E20:G20"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
